--- a/mlef_pipeline/results/DCR/HIGH_PDL1/training_summary.xlsx
+++ b/mlef_pipeline/results/DCR/HIGH_PDL1/training_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W12"/>
+  <dimension ref="A1:W5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,803 +548,292 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RWD</t>
+          <t>RWD_FMRAD</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6810581395348838</v>
+        <v>0.8361290322580645</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05166149141952969</v>
+        <v>0.06133886806050737</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5082076642970103</v>
+        <v>0.7207058498440891</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05791243626475871</v>
+        <v>0.08537651131291879</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3452432384251369</v>
+        <v>0.7691098259573712</v>
       </c>
       <c r="G2" t="n">
-        <v>0.09654636596259193</v>
+        <v>0.1151375884387798</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8050137454587613</v>
+        <v>0.7396240019696809</v>
       </c>
       <c r="I2" t="n">
-        <v>0.08637187051953316</v>
+        <v>0.1593464030453093</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7366666666666668</v>
+        <v>0.5046296296296297</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1340339081641193</v>
+        <v>0.2462529851191111</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4707854406130269</v>
+        <v>0.4570135746606335</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="N2" t="n">
-        <v>0.95</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6172413793103448</v>
+        <v>0.6291666666666667</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1416165058419505</v>
+        <v>0.2024806819930838</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2959183673469388</v>
+        <v>0.5241228070175439</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="T2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U2" t="n">
-        <v>422</v>
+        <v>162</v>
       </c>
       <c r="V2" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="W2" t="n">
-        <v>69</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RWD_DP</t>
+          <t>RWD_FMRAD/rwd-only</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7517708965796397</v>
+        <v>0.6777419354838708</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06842197034437836</v>
+        <v>0.08385599183429282</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6734125916455594</v>
+        <v>0.4087895939814021</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0508212342489197</v>
+        <v>0.09328463801558573</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7642562418424488</v>
+        <v>0.1614303487688501</v>
       </c>
       <c r="G3" t="n">
-        <v>0.08522368562204195</v>
+        <v>0.09692732807373153</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6125489203450223</v>
+        <v>0.9420878618409482</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1738361651993115</v>
+        <v>0.0320829497368184</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6335403726708078</v>
+        <v>0.673611111111111</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2322495218410949</v>
+        <v>0.2019847182177055</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4990723562152134</v>
+        <v>0.4976076555023923</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8695652173913043</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1428571428571428</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6155555555555555</v>
+        <v>0.6312500000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1718089747500454</v>
+        <v>0.204764794576755</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5904761904761904</v>
+        <v>0.5772727272727273</v>
       </c>
       <c r="R3" t="n">
-        <v>0.68</v>
+        <v>0.3125</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="T3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="U3" t="n">
-        <v>203</v>
+        <v>162</v>
       </c>
       <c r="V3" t="n">
         <v>30</v>
       </c>
       <c r="W3" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RWD_DP/rwd-only</t>
+          <t>RWD_DP_FMRAD</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.684274438372799</v>
+        <v>0.8596311475409837</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07345339168037535</v>
+        <v>0.07948265057060966</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5837115195189111</v>
+        <v>0.7569630278358932</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03562451355711808</v>
+        <v>0.1372189052778314</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6436613195233886</v>
+        <v>0.7466176296821458</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1029905502319659</v>
+        <v>0.1567609143374413</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5720762995125814</v>
+        <v>0.8667861409796894</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1501119808798309</v>
+        <v>0.1511087358697988</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5527950310559009</v>
+        <v>0.4038461538461537</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2908668101118612</v>
+        <v>0.2713621782457718</v>
       </c>
       <c r="L4" t="n">
-        <v>0.52</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9130434782608695</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1428571428571428</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7799999999999999</v>
+        <v>0.4848484848484848</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1392126589069852</v>
+        <v>0.2807494613696343</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.6293103448275862</v>
+        <v>0.4505494505494506</v>
       </c>
       <c r="R4" t="n">
-        <v>0.88</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="T4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="U4" t="n">
-        <v>203</v>
+        <v>93</v>
       </c>
       <c r="V4" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="W4" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RWD_FMRAD</t>
+          <t>RWD_DP_FMRAD/rwd-only</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8016326530612246</v>
+        <v>0.7059426229508197</v>
       </c>
       <c r="C5" t="n">
-        <v>0.06752046801881928</v>
+        <v>0.1077290265741907</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5723934250623326</v>
+        <v>0.5061758738236466</v>
       </c>
       <c r="E5" t="n">
-        <v>0.09178988163151601</v>
+        <v>0.1133685005377487</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7405491651205937</v>
+        <v>0.3130391114262082</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1760967897322043</v>
+        <v>0.1479799400962693</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5640952380952381</v>
+        <v>0.9408602150537635</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2835441479893354</v>
+        <v>0.0624096062701285</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6130434782608696</v>
+        <v>0.4615384615384617</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2181430309812649</v>
+        <v>0.4015528181142509</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5722222222222222</v>
+        <v>0.15</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4782608695652174</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5401785714285714</v>
+        <v>0.7070707070707071</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2197085882662899</v>
+        <v>0.2439609380290044</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.5488721804511278</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="T5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U5" t="n">
-        <v>175</v>
+        <v>93</v>
       </c>
       <c r="V5" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="W5" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>RWD_FMRAD/rwd-only</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.690748299319728</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.07848040767850495</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.3317001664722449</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.1168047332403506</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.5079109461966604</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.45070352004924</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.579047619047619</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.4435846558874366</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.7478260869565219</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.2147934708314063</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.5722222222222222</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.4782608695652174</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.71875</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.2047076910292157</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.4223363286264442</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="T6" t="n">
-        <v>10</v>
-      </c>
-      <c r="U6" t="n">
-        <v>175</v>
-      </c>
-      <c r="V6" t="n">
-        <v>33</v>
-      </c>
-      <c r="W6" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>RWD_PYRAD</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.7450652392104383</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.07595861286368288</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.6184892651664838</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.09717347937035196</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.7319887586451869</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.1583155554816373</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.5942604239459585</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.2285257231312487</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.6078431372549018</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.2192966760314161</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.6037267080745341</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.7058823529411765</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.5874999999999999</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.2101630779514705</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.5735449735449736</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.6875</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.4666666666666667</v>
-      </c>
-      <c r="T7" t="n">
-        <v>7</v>
-      </c>
-      <c r="U7" t="n">
-        <v>159</v>
-      </c>
-      <c r="V7" t="n">
-        <v>29</v>
-      </c>
-      <c r="W7" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>RWD_PYRAD/rwd-only</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.6589160254265641</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.08508016208638747</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.3724204467832931</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.1454886220912994</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.4433230949246746</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.4276220310159281</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.6497926857675286</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.4458726926799334</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.4509803921568627</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.2210237952013874</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.5120192307692308</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.3529411764705883</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.5125</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.2141464101863961</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.4363636363636363</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.1875</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="T8" t="n">
-        <v>10</v>
-      </c>
-      <c r="U8" t="n">
-        <v>159</v>
-      </c>
-      <c r="V8" t="n">
-        <v>29</v>
-      </c>
-      <c r="W8" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>RWD_DP_FMRAD</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.9430633520449079</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.04957254437057024</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.8793175959842627</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.1188289504128007</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.1781108779622537</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.8518518518518517</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.2143673500516709</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.8181818181818186</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.2011784353946343</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.7090909090909091</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.8181818181818182</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.5727272727272728</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.2625808793312006</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.6181818181818182</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.6363636363636364</v>
-      </c>
-      <c r="T9" t="n">
-        <v>11</v>
-      </c>
-      <c r="U9" t="n">
-        <v>72</v>
-      </c>
-      <c r="V9" t="n">
-        <v>16</v>
-      </c>
-      <c r="W9" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>RWD_DP_FMRAD/rwd-only</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.63672814755413</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.1297943028064106</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.2901120683378748</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.07812997214790009</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.5388888888888889</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.4304973078879419</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.4530418452861136</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.3919927969080108</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.2380952380952381</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.2727272727272727</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.5727272727272728</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.2747264319682625</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.5227272727272727</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.5454545454545454</v>
-      </c>
-      <c r="T10" t="n">
-        <v>10</v>
-      </c>
-      <c r="U10" t="n">
-        <v>72</v>
-      </c>
-      <c r="V10" t="n">
-        <v>16</v>
-      </c>
-      <c r="W10" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>RWD_DP_PYRAD</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.8209677419354839</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.09322672570117008</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.7200262929888224</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.1030401978776811</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.8279555609225938</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.1793321711877441</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.6720390720390721</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.2076109993674974</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.4807692307692308</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.3423510952967899</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.4333333333333333</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.6153846153846154</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.686868686868687</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.2544590596487172</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.6491228070175439</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.6363636363636364</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="T11" t="n">
-        <v>10</v>
-      </c>
-      <c r="U11" t="n">
-        <v>91</v>
-      </c>
-      <c r="V11" t="n">
-        <v>17</v>
-      </c>
-      <c r="W11" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>RWD_DP_PYRAD/rwd-only</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.5416666666666665</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.1183774379571272</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.340493665965105</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.09971930491189082</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.702451394759087</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.3891603190083057</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.2466422466422466</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.383771386310661</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.1442307692307692</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.2696114362380859</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.2245614035087719</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.2307692307692308</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.6414141414141415</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0.2615702653449413</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.595959595959596</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.6363636363636364</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="T12" t="n">
-        <v>10</v>
-      </c>
-      <c r="U12" t="n">
-        <v>91</v>
-      </c>
-      <c r="V12" t="n">
-        <v>17</v>
-      </c>
-      <c r="W12" t="n">
         <v>20</v>
       </c>
     </row>

--- a/mlef_pipeline/results/DCR/HIGH_PDL1/training_summary.xlsx
+++ b/mlef_pipeline/results/DCR/HIGH_PDL1/training_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:W12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,292 +548,803 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RWD_FMRAD</t>
+          <t>RWD</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8361290322580645</v>
+        <v>0.6795697674418604</v>
       </c>
       <c r="C2" t="n">
-        <v>0.06133886806050737</v>
+        <v>0.05161213363521344</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7207058498440891</v>
+        <v>0.4793809878720441</v>
       </c>
       <c r="E2" t="n">
-        <v>0.08537651131291879</v>
+        <v>0.1095796660384835</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7691098259573712</v>
+        <v>0.2807070314090898</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1151375884387798</v>
+        <v>0.1153248011797558</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7396240019696809</v>
+        <v>0.8526668367378465</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1593464030453093</v>
+        <v>0.06355720135412796</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5046296296296297</v>
+        <v>0.74</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2462529851191111</v>
+        <v>0.1348444865808242</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4570135746606335</v>
+        <v>0.4106836559666748</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5</v>
+        <v>0.1777777777777778</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4166666666666667</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6291666666666667</v>
+        <v>0.6241379310344828</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2024806819930838</v>
+        <v>0.1382572045454311</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5241228070175439</v>
+        <v>0.2959183673469388</v>
       </c>
       <c r="R2" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U2" t="n">
-        <v>162</v>
+        <v>422</v>
       </c>
       <c r="V2" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="W2" t="n">
-        <v>31</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RWD_FMRAD/rwd-only</t>
+          <t>RWD_DP</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6777419354838708</v>
+        <v>0.7661404573972881</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08385599183429282</v>
+        <v>0.06580306308971196</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4087895939814021</v>
+        <v>0.6812268189984537</v>
       </c>
       <c r="E3" t="n">
-        <v>0.09328463801558573</v>
+        <v>0.05331070169889827</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1614303487688501</v>
+        <v>0.7724664224664226</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09692732807373153</v>
+        <v>0.091268506733507</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9420878618409482</v>
+        <v>0.6121919559700669</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0320829497368184</v>
+        <v>0.1558253565099042</v>
       </c>
       <c r="J3" t="n">
-        <v>0.673611111111111</v>
+        <v>0.6770186335403727</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2019847182177055</v>
+        <v>0.2153641243795226</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4976076555023923</v>
+        <v>0.4990723562152134</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.8695652173913043</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6312500000000001</v>
+        <v>0.6288888888888889</v>
       </c>
       <c r="P3" t="n">
-        <v>0.204764794576755</v>
+        <v>0.1700047275654991</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5772727272727273</v>
+        <v>0.5622171945701357</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3125</v>
+        <v>0.68</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="T3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="U3" t="n">
-        <v>162</v>
+        <v>203</v>
       </c>
       <c r="V3" t="n">
         <v>30</v>
       </c>
       <c r="W3" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RWD_DP_FMRAD</t>
+          <t>RWD_DP/rwd-only</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8596311475409837</v>
+        <v>0.6367132159481885</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07948265057060966</v>
+        <v>0.07772882052922758</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7569630278358932</v>
+        <v>0.5509035993696912</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1372189052778314</v>
+        <v>0.04973702497065574</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7466176296821458</v>
+        <v>0.6286219527598839</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1567609143374413</v>
+        <v>0.1712367035513515</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8667861409796894</v>
+        <v>0.5451014752364078</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1511087358697988</v>
+        <v>0.2014223035054775</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4038461538461537</v>
+        <v>0.5590062111801244</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2713621782457718</v>
+        <v>0.2707479863853941</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.542483660130719</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.9565217391304348</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4848484848484848</v>
+        <v>0.6977777777777777</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2807494613696343</v>
+        <v>0.1651934145940281</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4505494505494506</v>
+        <v>0.6490897677338355</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.92</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="T4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U4" t="n">
-        <v>93</v>
+        <v>203</v>
       </c>
       <c r="V4" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="W4" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>RWD_FMRAD</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.8361290322580645</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.06133886806050737</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.7207058498440891</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.08537651131291879</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.7691098259573712</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.1151375884387798</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.7396240019696809</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.1593464030453093</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5046296296296297</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.2462529851191111</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.4570135746606335</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.6291666666666667</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.2024806819930838</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.5241228070175439</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="T5" t="n">
+        <v>9</v>
+      </c>
+      <c r="U5" t="n">
+        <v>162</v>
+      </c>
+      <c r="V5" t="n">
+        <v>30</v>
+      </c>
+      <c r="W5" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RWD_FMRAD/rwd-only</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.6777419354838708</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.08385599183429282</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.4087895939814021</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.09328463801558573</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1614303487688501</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.09692732807373153</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.9420878618409482</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.0320829497368184</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.673611111111111</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.2019847182177055</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.4976076555023923</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.6312500000000001</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.204764794576755</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.5772727272727273</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="T6" t="n">
+        <v>7</v>
+      </c>
+      <c r="U6" t="n">
+        <v>162</v>
+      </c>
+      <c r="V6" t="n">
+        <v>30</v>
+      </c>
+      <c r="W6" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RWD_PYRAD</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.7336901973904316</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.07849557706699928</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.5578283364396723</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.0571811989182594</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.7043346079107378</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.2013641033326801</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.5066620079198695</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.2019640814368093</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.4901960784313726</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.234154677418146</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.315527950310559</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.1176470588235294</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.6208333333333333</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.2158863257495722</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.6743697478991597</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T7" t="n">
+        <v>7</v>
+      </c>
+      <c r="U7" t="n">
+        <v>159</v>
+      </c>
+      <c r="V7" t="n">
+        <v>29</v>
+      </c>
+      <c r="W7" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RWD_PYRAD/rwd-only</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.6565741050518569</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.08548439203695557</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.3387523404061403</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.1291178337209305</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4234313295304958</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.4421265487659403</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6415094339622641</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.4696180552699488</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.4068627450980393</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.2170369157052704</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.3655083655083655</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.1176470588235294</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.5291666666666668</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.2153383975059006</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.3260869565217391</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>10</v>
+      </c>
+      <c r="U8" t="n">
+        <v>159</v>
+      </c>
+      <c r="V8" t="n">
+        <v>29</v>
+      </c>
+      <c r="W8" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RWD_DP_FMRAD</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.8596311475409837</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.07948265057060966</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.7569630278358932</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.1372189052778314</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.7466176296821458</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.1567609143374413</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.8667861409796894</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1511087358697988</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.4038461538461537</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.2713621782457718</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.5384615384615384</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.4848484848484848</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.2807494613696342</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.4505494505494506</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="T9" t="n">
+        <v>11</v>
+      </c>
+      <c r="U9" t="n">
+        <v>93</v>
+      </c>
+      <c r="V9" t="n">
+        <v>17</v>
+      </c>
+      <c r="W9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>RWD_DP_FMRAD/rwd-only</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B10" t="n">
         <v>0.7059426229508197</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C10" t="n">
         <v>0.1077290265741907</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D10" t="n">
         <v>0.5061758738236466</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E10" t="n">
         <v>0.1133685005377487</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F10" t="n">
         <v>0.3130391114262082</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G10" t="n">
         <v>0.1479799400962693</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H10" t="n">
         <v>0.9408602150537635</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I10" t="n">
         <v>0.0624096062701285</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J10" t="n">
         <v>0.4615384615384617</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K10" t="n">
         <v>0.4015528181142509</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L10" t="n">
         <v>0.15</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M10" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N10" t="n">
         <v>0.75</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O10" t="n">
         <v>0.7070707070707071</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P10" t="n">
         <v>0.2439609380290044</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q10" t="n">
         <v>0.5488721804511278</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R10" t="n">
         <v>0.4545454545454545</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S10" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T10" t="n">
         <v>10</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U10" t="n">
         <v>93</v>
       </c>
-      <c r="V5" t="n">
+      <c r="V10" t="n">
         <v>17</v>
       </c>
-      <c r="W5" t="n">
+      <c r="W10" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RWD_DP_PYRAD</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.8139784946236559</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.09282317656772321</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.7147756184701998</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.1171798697136201</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.7742845067020891</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1593044739398784</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.698901098901099</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1977560657098638</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.4230769230769229</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.3357164318279052</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.4333333333333333</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.6464646464646465</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.2638361962868299</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.6419437340153453</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="T11" t="n">
+        <v>6</v>
+      </c>
+      <c r="U11" t="n">
+        <v>91</v>
+      </c>
+      <c r="V11" t="n">
+        <v>17</v>
+      </c>
+      <c r="W11" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RWD_DP_PYRAD/rwd-only</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.6489247311827957</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.1112047767497558</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.439839449961722</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.06597060555407371</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.744378698224852</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.2663336706203931</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.3272283272283272</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.3818436085741609</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.2307692307692308</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.4091464893446104</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.2714285714285715</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.6464646464646465</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.2631202972626482</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="T12" t="n">
+        <v>10</v>
+      </c>
+      <c r="U12" t="n">
+        <v>91</v>
+      </c>
+      <c r="V12" t="n">
+        <v>17</v>
+      </c>
+      <c r="W12" t="n">
         <v>20</v>
       </c>
     </row>
